--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260930.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260930.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>9.97%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.80%</t>
+          <t>8.77%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.25%</t>
+          <t>8.28%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>8.06%</t>
+          <t>8.04%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.06%</t>
+          <t>7.09%</t>
         </is>
       </c>
     </row>
@@ -726,51 +726,51 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>5.96%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>24,757,000</t>
+          <t>7,389,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.78%</t>
+          <t>4.90%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>7,389,000</t>
+          <t>24,757,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.78%</t>
+          <t>4.76%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>4.72%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.57%</t>
+          <t>4.49%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>4.20%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>3.90%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>12,966,000</t>
+          <t>12,526,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,022,000</t>
+          <t>2,483,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1261,39 +1261,39 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,740,000</t>
+          <t>3,921,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,921,000</t>
+          <t>1,740,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>8,773,373,263</t>
+          <t>13,665,898,552</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>2,094,635,197</t>
+          <t>2,169,189,397</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>7,063,520,391</t>
+          <t>-402,825,280</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>3,005,175,390</t>
+          <t>2,955,175,390</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
